--- a/output/pdf_financials_xlsx/STLR.xlsx
+++ b/output/pdf_financials_xlsx/STLR.xlsx
@@ -1444,31 +1444,31 @@
         <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-1.385287</v>
+        <v>-10.565635</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.091218</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.409832</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.879184</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-1.635462</v>
+        <v>-11.143822</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.750726</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0.5333329999999999</v>
+        <v>-7.216989</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-1.399836</v>
+        <v>-28.489218</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-4.2609</v>
+        <v>-41.848938</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -1696,31 +1696,31 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>4.590174</v>
+        <v>-4.590174</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.545609</v>
+        <v>-2.545609</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.704916</v>
+        <v>-0.704916</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.939592</v>
+        <v>-2.939592</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.75418</v>
+        <v>-4.75418</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.875363</v>
+        <v>-3.875363</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>3.341828</v>
+        <v>-3.341828</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>13.544691</v>
+        <v>-13.544691</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>18.794019</v>
+        <v>-18.794019</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-16.212636</v>
@@ -1884,31 +1884,31 @@
         <v>3.845036</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>4.590174</v>
+        <v>-4.590174</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.545609</v>
+        <v>-2.545609</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.704916</v>
+        <v>-0.704916</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.939592</v>
+        <v>-2.939592</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4.75418</v>
+        <v>-4.75418</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.875363</v>
+        <v>-3.875363</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>3.341828</v>
+        <v>-3.341828</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>13.544691</v>
+        <v>-13.544691</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>18.794019</v>
+        <v>-18.794019</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-16.212636</v>
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>229.5087</v>
+        <v>-229.5087</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>237.709</v>
+        <v>-237.709</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>193.76815</v>
+        <v>-193.76815</v>
       </c>
       <c r="M26" s="1" t="inlineStr">
         <is>
@@ -2464,31 +2464,31 @@
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>23.18293099059637</v>
+        <v>176.8170690094036</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>25.59551849696743</v>
+        <v>174.4044815030326</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>13.76286043341167</v>
+        <v>186.2371395665883</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>9.366880597826883</v>
+        <v>190.6331194021731</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>18.48152231634386</v>
+        <v>181.5184776836561</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -45693,10 +45693,10 @@
         </is>
       </c>
       <c r="Q370" s="5" t="n">
-        <v>13.544691</v>
+        <v>-13.544691</v>
       </c>
       <c r="R370" s="5" t="n">
-        <v>18.794019</v>
+        <v>-18.794019</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -46806,25 +46806,25 @@
         </is>
       </c>
       <c r="J382" s="5" t="n">
-        <v>4.590174</v>
+        <v>-4.590174</v>
       </c>
       <c r="K382" s="5" t="n">
-        <v>2.545609</v>
+        <v>-2.545609</v>
       </c>
       <c r="L382" s="5" t="n">
-        <v>0.704916</v>
+        <v>-0.704916</v>
       </c>
       <c r="M382" s="5" t="n">
-        <v>2.939592</v>
+        <v>-2.939592</v>
       </c>
       <c r="N382" s="5" t="n">
-        <v>4.75418</v>
+        <v>-4.75418</v>
       </c>
       <c r="O382" s="5" t="n">
-        <v>3.875363</v>
+        <v>-3.875363</v>
       </c>
       <c r="P382" s="5" t="n">
-        <v>3.341828</v>
+        <v>-3.341828</v>
       </c>
       <c r="Q382" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/STLR.xlsx
+++ b/output/pdf_financials_xlsx/STLR.xlsx
@@ -1118,37 +1118,37 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.03527</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015376</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.081955</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015307</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003284</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035854</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.060848</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.032625</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.050415</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.068138</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.230979</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -2174,37 +2174,37 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.977647</v>
+        <v>6.012917</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.845036</v>
+        <v>3.860412</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>5.975461</v>
+        <v>6.057416</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.545609</v>
+        <v>2.560916</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.704916</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.939592</v>
+        <v>2.975446</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>6.389642</v>
+        <v>6.45049</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.875363</v>
+        <v>3.907988</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>3.875161</v>
+        <v>3.925576</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>14.944527</v>
+        <v>15.012665</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>23.054919</v>
+        <v>23.285898</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-16.212636</v>
@@ -2302,37 +2302,37 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.977647</v>
+        <v>6.012917</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.845036</v>
+        <v>3.860412</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.975461</v>
+        <v>6.057416</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.545609</v>
+        <v>2.560916</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.704916</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.939592</v>
+        <v>2.975446</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>6.389642</v>
+        <v>6.45049</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.875363</v>
+        <v>3.907988</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>3.875161</v>
+        <v>3.925576</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.944527</v>
+        <v>15.012665</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>23.054919</v>
+        <v>23.285898</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-16.106577</v>
@@ -9626,7 +9626,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -12486,7 +12490,11 @@
           <t>Reclamation deposits 6 192,064</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -17065,7 +17073,11 @@
           <t>Reclamation deposits 5, 14</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -45342,7 +45354,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">

--- a/output/pdf_financials_xlsx/STLR.xlsx
+++ b/output/pdf_financials_xlsx/STLR.xlsx
@@ -7805,19 +7805,19 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>0.12279</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>5.758485</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>1.436979</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>6.370926</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>10.219841</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -39628,7 +39628,11 @@
           <t>Issuance of common shares, net of issue costs 4</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -40612,7 +40616,11 @@
           <t>Issuance of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E319" s="5" t="n">
         <v>0.12279</v>
       </c>

--- a/output/pdf_financials_xlsx/STLR.xlsx
+++ b/output/pdf_financials_xlsx/STLR.xlsx
@@ -7255,16 +7255,16 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.002801</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.026507</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>-0.068505</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.145669</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>0</v>
@@ -33494,7 +33494,11 @@
           <t>Accretion expense 10</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -35413,7 +35417,11 @@
           <t>Accretion expense 8</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -40816,7 +40824,11 @@
           <t>Recovery of future income taxes</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E321" s="5" t="n">
         <v>-0.409293</v>
       </c>
